--- a/artfynd/A 55408-2023 artfynd.xlsx
+++ b/artfynd/A 55408-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55408-2023 artfynd.xlsx
+++ b/artfynd/A 55408-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113402005</v>
+        <v>113401324</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skaftet (Skaftet), Sm</t>
+          <t>Skaftet, Skaftet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594861</v>
+        <v>594813</v>
       </c>
       <c r="R2" t="n">
-        <v>6390436</v>
+        <v>6390479</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113402205</v>
+        <v>113402005</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,14 +815,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skaftet (Skaftet), Sm</t>
+          <t>Skaftet, Skaftet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594796</v>
+        <v>594861</v>
       </c>
       <c r="R3" t="n">
-        <v>6390493</v>
+        <v>6390436</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113401324</v>
+        <v>113402205</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,14 +923,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skaftet (Skaftet), Sm</t>
+          <t>Skaftet, Skaftet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594813</v>
+        <v>594796</v>
       </c>
       <c r="R4" t="n">
-        <v>6390479</v>
+        <v>6390493</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,12 +1002,7 @@
         <v>113402288</v>
       </c>
       <c r="B5" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,7 +1031,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skaftet (Skaftet), Sm</t>
+          <t>Skaftet, Skaftet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1127,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113402108</v>
+        <v>113410029</v>
       </c>
       <c r="B6" t="n">
-        <v>90292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1118,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skaftet (Skaftet), Sm</t>
+          <t>Hjältemaren, Hjältemaren, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594827</v>
+        <v>594829</v>
       </c>
       <c r="R6" t="n">
-        <v>6390450</v>
+        <v>6390411</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1200,12 +1182,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1206,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113410029</v>
+        <v>113402108</v>
       </c>
       <c r="B7" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1249,44 +1235,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hjältemaren (Hjältemaren), Sm</t>
+          <t>Skaftet, Skaftet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594829</v>
+        <v>594827</v>
       </c>
       <c r="R7" t="n">
-        <v>6390411</v>
+        <v>6390450</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1313,22 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,6 +1306,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
